--- a/public/importFile.xlsx
+++ b/public/importFile.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\15562\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5B871D-05C5-416D-89BF-C487005873CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="18350" windowHeight="6880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$29</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="102">
   <si>
     <t>数据库名</t>
   </si>
@@ -35,13 +46,310 @@
   </si>
   <si>
     <t>字段注释</t>
+  </si>
+  <si>
+    <t>OA_Enterprise_DB</t>
+  </si>
+  <si>
+    <t>OA_Employee_Master</t>
+  </si>
+  <si>
+    <t>OA 系统员工核心信息表，支撑人事、考勤、权限等模块</t>
+  </si>
+  <si>
+    <t>emp_id</t>
+  </si>
+  <si>
+    <t>员工工号，OA 系统唯一标识，格式：部门简码 + 6 位数字</t>
+  </si>
+  <si>
+    <t>emp_name</t>
+  </si>
+  <si>
+    <t>员工姓名，与劳动合同、身份证件一致</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>员工性别，枚举值：男 / 女 / 用于人事统计</t>
+  </si>
+  <si>
+    <t>date_of_birth</t>
+  </si>
+  <si>
+    <t>出生日期，格式：YYYY-MM-DD，用于退休年龄计算</t>
+  </si>
+  <si>
+    <t>id_card_no</t>
+  </si>
+  <si>
+    <t>身份证号，用于身份核验和社保办理</t>
+  </si>
+  <si>
+    <t>entry_date</t>
+  </si>
+  <si>
+    <t>入职日期，格式：YYYY-MM-DD，OA 账号开通依据</t>
+  </si>
+  <si>
+    <t>probation_end_date</t>
+  </si>
+  <si>
+    <t>试用期结束日期，格式：YYYY-MM-DD，转正流程触发点</t>
+  </si>
+  <si>
+    <t>emp_status</t>
+  </si>
+  <si>
+    <t>员工状态，枚举值：试用 / 正式 / 待离职 / 已离职，控制 OA 权限</t>
+  </si>
+  <si>
+    <t>dept_id</t>
+  </si>
+  <si>
+    <t>所属部门 ID，关联部门表，用于组织架构展示</t>
+  </si>
+  <si>
+    <t>dept_name</t>
+  </si>
+  <si>
+    <t>所属部门名称，冗余存储，优化查询效率</t>
+  </si>
+  <si>
+    <t>direct_supervisor_id</t>
+  </si>
+  <si>
+    <t>直属上级工号，关联员工表，用于审批流和汇报关系</t>
+  </si>
+  <si>
+    <t>direct_supervisor_name</t>
+  </si>
+  <si>
+    <t>直属上级姓名，冗余存储，用于审批单显示</t>
+  </si>
+  <si>
+    <t>company_email</t>
+  </si>
+  <si>
+    <t>企业邮箱，OA 登录账号，格式：工号 @企业域名</t>
+  </si>
+  <si>
+    <t>enterprise_wechat</t>
+  </si>
+  <si>
+    <t>企业微信账号，用于 OA 消息推送和协作</t>
+  </si>
+  <si>
+    <t>work_phone</t>
+  </si>
+  <si>
+    <t>办公座机，格式：分机号 / 总机号 - 分机号</t>
+  </si>
+  <si>
+    <t>mobile_phone</t>
+  </si>
+  <si>
+    <t>个人手机号，用于 OA 登录验证和紧急通知</t>
+  </si>
+  <si>
+    <t>employment_type</t>
+  </si>
+  <si>
+    <t>用工类型，枚举值：正式合同 / 劳务派遣 / 实习，关联社保缴纳</t>
+  </si>
+  <si>
+    <t>contract_type</t>
+  </si>
+  <si>
+    <t>合同类型，枚举值：固定期限 / 无固定期限，用于合同管理模块</t>
+  </si>
+  <si>
+    <t>contract_start_date</t>
+  </si>
+  <si>
+    <t>合同开始日期，格式：YYYY-MM-DD，合同有效期计算依据</t>
+  </si>
+  <si>
+    <t>contract_end_date</t>
+  </si>
+  <si>
+    <t>合同结束日期，格式：YYYY-MM-DD（无固定期限填 “长期”）</t>
+  </si>
+  <si>
+    <t>bank_name</t>
+  </si>
+  <si>
+    <t>工资卡开户行，如：中国工商银行 XX 支行</t>
+  </si>
+  <si>
+    <t>bank_account_no</t>
+  </si>
+  <si>
+    <t>工资卡账号，加密存储，用于薪资发放</t>
+  </si>
+  <si>
+    <t>highest_education</t>
+  </si>
+  <si>
+    <t>最高学历，枚举值：专科 / 本科 / 硕士 / 博士，用于人事档案管理</t>
+  </si>
+  <si>
+    <t>graduation_school</t>
+  </si>
+  <si>
+    <t>毕业院校，用于人才盘点和培训需求分析</t>
+  </si>
+  <si>
+    <t>professional_qualification</t>
+  </si>
+  <si>
+    <t>职业资格证书，如：PMP/CPA，用于技能库管理</t>
+  </si>
+  <si>
+    <t>oa_role_id</t>
+  </si>
+  <si>
+    <t>OA 角色 ID，关联角色表，控制菜单和操作权限</t>
+  </si>
+  <si>
+    <t>oa_role_name</t>
+  </si>
+  <si>
+    <t>OA 角色名称，如：普通员工 / 部门经理 / 系统管理员</t>
+  </si>
+  <si>
+    <t>account_status</t>
+  </si>
+  <si>
+    <t>OA 账号状态，枚举值：正常 / 锁定 / 禁用，控制登录权限</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>OA_System_DB</t>
+  </si>
+  <si>
+    <t>OA_Employee_Info</t>
+  </si>
+  <si>
+    <t>OA 系统员工个人信息主表，存储员工全量个人及工作相关信息</t>
+  </si>
+  <si>
+    <t>employee_id</t>
+  </si>
+  <si>
+    <t>员工唯一标识 ID，OA 系统内唯一，自增主键</t>
+  </si>
+  <si>
+    <t>employee_name</t>
+  </si>
+  <si>
+    <t>员工姓名，与身份证件、劳动合同姓名一致</t>
+  </si>
+  <si>
+    <t>员工性别，枚举值：男 / 女 / 未知</t>
+  </si>
+  <si>
+    <t>员工出生日期，格式：YYYY-MM-DD，用于计算年龄及退休时间</t>
+  </si>
+  <si>
+    <t>id_type</t>
+  </si>
+  <si>
+    <t>身份证件类型，枚举值：居民身份证 / 护照 / 港澳通行证 / 台湾通行证</t>
+  </si>
+  <si>
+    <t>id_number</t>
+  </si>
+  <si>
+    <t>身份证件号码，加密存储，用于身份核验及社保公积金办理</t>
+  </si>
+  <si>
+    <t>员工手机号码，用于 OA 消息通知、考勤验证及紧急联系</t>
+  </si>
+  <si>
+    <t>公司分配的企业邮箱，格式：姓名首字母 + 工号 @公司域名，用于公务沟通</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>员工所属部门，关联 OA 部门表，用于流程审批及组织架构展示</t>
+  </si>
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>员工岗位名称，如：产品经理 / 前端开发工程师 / 人力资源专员</t>
+  </si>
+  <si>
+    <t>hire_date</t>
+  </si>
+  <si>
+    <t>员工入职日期，格式：YYYY-MM-DD，用于计算工龄及试用期管理</t>
+  </si>
+  <si>
+    <t>用工类型，枚举值：正式员工 / 试用期员工 / 实习生 / 劳务派遣 / 外包</t>
+  </si>
+  <si>
+    <t>education_level</t>
+  </si>
+  <si>
+    <t>最高学历，枚举值：小学 / 初中 / 高中 / 中专 / 大专 / 本科 / 硕士 / 博士 / 其他</t>
+  </si>
+  <si>
+    <t>最高学历毕业院校名称，如：北京大学 / 清华大学</t>
+  </si>
+  <si>
+    <t>emergency_contact_name</t>
+  </si>
+  <si>
+    <t>紧急联系人姓名，用于员工突发情况联系</t>
+  </si>
+  <si>
+    <t>emergency_contact_phone</t>
+  </si>
+  <si>
+    <t>紧急联系人手机号码，确保 24 小时可接通</t>
+  </si>
+  <si>
+    <t>residential_address</t>
+  </si>
+  <si>
+    <t>员工常住地址，含省市区详细信息，用于邮寄办公用品或通知</t>
+  </si>
+  <si>
+    <t>social_security_number</t>
+  </si>
+  <si>
+    <t>社保编号，用于 OA 系统中社保缴纳查询及相关业务办理</t>
+  </si>
+  <si>
+    <t>employee_status</t>
+  </si>
+  <si>
+    <t>员工状态，枚举值：在职 / 离职 / 待入职 / 休假 / 停薪留职</t>
+  </si>
+  <si>
+    <t>last_update_time</t>
+  </si>
+  <si>
+    <t>信息最后更新时间，格式：YYYY-MM-DD HH:MM:SS，用于数据追溯</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -50,22 +358,159 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -78,13 +523,214 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -102,178 +748,357 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -284,7 +1109,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -312,157 +1137,157 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>483870</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>45085</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="矩形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8169910" y="652780"/>
-          <a:ext cx="2890520" cy="1099185"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
-            <a:t>填写说明：</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
-            <a:t>1</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
-            <a:t>、黄色底色列为必填项，其余列可选填。</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
-            <a:t>2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
-            <a:t>、样例：</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
-            <a:t>COREDB</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
-            <a:t>、</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
-            <a:t>CUST_INFO</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
-            <a:t>、客户信息表、</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
-            <a:t>CUST_NAME</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
-            <a:t>、客户名称</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -709,52 +1534,953 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9.265625" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultColWidth="45.3636363636364" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="5" width="14.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6363636363636" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.6363636363636" style="3" customWidth="1"/>
+    <col min="3" max="3" width="43.6363636363636" style="3" customWidth="1"/>
+    <col min="4" max="4" width="23.6363636363636" style="3" customWidth="1"/>
+    <col min="5" max="5" width="44.6363636363636" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="45.3636363636364" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" ht="28" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="28" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" ht="28" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" ht="28" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" ht="28" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" ht="28" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="28" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" ht="28" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" ht="28" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" ht="28" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" ht="28" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" ht="28" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" ht="28" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" ht="28" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" ht="28" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" ht="28" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" ht="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" ht="28" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E29" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="1" ht="28.75" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+    <row r="2" ht="112.75" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" ht="112.75" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" ht="112.75" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" ht="112.75" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" ht="112.75" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" ht="112.75" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" ht="112.75" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" ht="126.75" spans="1:6">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" ht="112.75" spans="1:6">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" ht="112.75" spans="1:6">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" ht="112.75" spans="1:6">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" ht="126.75" spans="1:6">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" ht="154.75" spans="1:6">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" ht="112.75" spans="1:6">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" ht="112.75" spans="1:6">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" ht="112.75" spans="1:6">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" ht="112.75" spans="1:6">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" ht="112.75" spans="1:6">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" ht="112.75" spans="1:6">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" ht="126.75" spans="1:6">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <headerFooter/>
 </worksheet>
 </file>